--- a/tm90.xlsx
+++ b/tm90.xlsx
@@ -425,923 +425,1670 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>As a patient</t>
+          <t>Scenario ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>I want to view my upcoming appointments in the patient portal</t>
+          <t>Scenario Title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>So that I can keep track of my scheduled consultations and avoid missing appointments.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Automation Feasible</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Step #</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Test Step Description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>- Appointment status (Confirmed</t>
+          <t>TC001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cancelled) AC3 No Upcoming Appointments Given the patient has no upcoming appointments When they open the "My Appointments" page Then the system should display the message: "You have no upcoming appointments." AC4 Cancelled Appointments Given an appointment has been cancelled When the patient views their appointments Then the appointment should display the status as Cancelled and should not allow online check-in. AC5 Security Given a user is logged in When they access the appointments page Then they should only see appointments associated with their own patient account. AC6 Performance Given the patient has up to 100 upcoming appointments When the appointments page loads Then the page should display all appointments within 3 seconds under normal network conditions. # TEST SCENARIOS FOR WORK ITEM: 1571 - **Feature Title:** Display Upcoming Patient Appointments ## 1. Functional / Happy Path Scenarios</t>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Verify side-by-side plan comparison</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>User is logged into the CareSource enrollment portal and has completed the health needs questionnaire</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>User with completed profile and at least two recommended plans</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>System displays side-by-side comparison of at least two plans highlighting premiums, deductibles, co-pays, out-of-pocket maximums, and coverage for specified medications and doctors</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>- TS_001: Verify that a logged-in patient can navigate to the "My Appointments" page and view all upcoming appointments associated with their account</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>sorted by appointment date and time in ascending order (Covers Acceptance Criteria 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Review plan features and select a plan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Selected plan is highlighted and user can proceed to enrollment</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>- TS_002: Verify that each displayed upcoming appointment includes the doctor's name</t>
+          <t>TC002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>appointment date</t>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Verify navigation to enrollment after plan selection</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>User is on the plan comparison page</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>User with at least one recommended plan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Select a plan and click 'Enroll'</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>System transitions to the enrollment process with the chosen plan pre-selected</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>- TS_003: Verify that appointment date and time are displayed in the logged-in user's local time zone for all upcoming appointments (Covers Acceptance Criteria 1</t>
+          <t>TC003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>- TS_004: Verify that a cancelled upcoming appointment remains visible in the upcoming appointments list until its scheduled appointment time has passed and is marked with status "Cancelled" (Covers Acceptance Criteria 4) - TS_005: Verify that online check-in is not available for appointments with status "Cancelled" while other valid upcoming appointments continue to display according to business rules (Covers Acceptance Criteria 4)</t>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Negative - No recommended plans</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>User has completed health needs but no plans match criteria</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>User with uncommon criteria resulting in no matches</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>System displays a message: "No plans match your criteria. Please adjust your preferences."</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>- TS_006: Verify that the appointments page displays the statuses Confirmed</t>
+          <t>TC004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>and Cancelled correctly based on the latest information returned by the scheduling system (Covers Acceptance Criteria 2 - TS_007: Verify that a patient with no upcoming appointments sees the message "You have no upcoming appointments." on the "My Appointments" page (Covers Acceptance Criteria 3) ## 2. Negative &amp; Data Validation Scenarios - TS_008: Verify that past appointments are not displayed in the "Upcoming Appointments" list even if they exist in the patient's appointment history (Covers Acceptance Criteria 1) - TS_009: Verify that a logged-in user cannot view appointments belonging to another patient account when accessing the appointments page (Covers Acceptance Criteria 5)</t>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Edge - Maximum number of plans</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>User qualifies for 10+ plans</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>User with broad criteria resulting in maximum recommendations</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>System displays all recommended plans in a scrollable, readable format without UI breakage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- TS_010: Verify system behavior when appointment status information changes in the scheduling system before page load</t>
+          <t>TC005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ensuring the portal reflects the latest status rather than stale data (Covers Acceptance Criteria 2</t>
+          <t>US32274</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verify member can input medications and providers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medication: Metformin 500mg, Provider: Dr. Smith</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Navigate to health needs input page</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>System displays input fields for medications and providers</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>- TS_011: Verify system behavior when one or more appointment detail fields are missing or incomplete from the source system</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ensuring the page handles the data gracefully without exposing incorrect appointment information (Covers Acceptance Criteria 2)</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enter medication and provider information and submit</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>System accepts input, validates data, and confirms successful entry</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>- TS_012: Verify system behavior when online check-in is attempted directly for a cancelled appointment</t>
+          <t>TC006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ensuring the action is blocked (Covers Acceptance Criteria 4)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Verify financial preference input</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Premium: $200, Deductible: $1000, OOP Max: $5000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Navigate to financial preferences section</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>System displays fields for premium, deductible, and out-of-pocket maximum</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- TS_013: Verify system behavior when the user is authenticated but attempts to access the appointments page for a different patient context through URL manipulation</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>session switching</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>or other unauthorized means ## 3. Edge Case &amp; Boundary Scenarios - TS_014: Verify that the appointments page loads and displays up to 100 upcoming appointments within 3 seconds under normal network conditions (Covers Acceptance Criteria 6)</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Enter preferences and submit</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>System saves preferences and updates recommendation criteria</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>- TS_015: Verify that exactly 100 upcoming appointments are displayed completely and remain sorted in ascending date/time order without truncation or duplication (Covers Acceptance Criteria 1</t>
+          <t>TC007</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Negative - Invalid medication entry</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Medication: "" (blank entry)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Leave medication field blank and submit</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>System displays error: "Medication name required"</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>- TS_016: Verify system behavior when a patient has a single upcoming appointment</t>
+          <t>TC008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ensuring it displays correctly with all required appointment details (Covers Acceptance Criteria 1</t>
+          <t>US32274</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Edge - Large medication list</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Medication: 20+ entries</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Enter 20+ medications and submit</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>System accepts all entries and processes recommendations without error</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- TS_017: Verify system behavior when multiple upcoming appointments have closely spaced or identical times</t>
+          <t>TC009</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ensuring they are still displayed in ascending order consistently (Covers Acceptance Criteria 1)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Verify guided workflow for plan selection</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Health: Asthma, PCP: Dr. Lee, Premium: $150</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Start guided enrollment</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>System prompts for health data, provider, and financial preferences in sequence</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- TS_018: Verify that a cancelled appointment is visible immediately before its scheduled appointment time and no longer appears once that scheduled time has passed</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>in accordance with upcoming appointment rules (Covers Acceptance Criteria 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Complete all steps and submit</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>System generates and displays personalized plan recommendations with comparison tool</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- TS_019: Verify that appointments occurring near local time zone boundaries</t>
+          <t>TC010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>such as midnight or daylight saving time changes</t>
+          <t>US32273</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>are displayed with the correct local date/time and are classified correctly as upcoming or past (Covers Acceptance Criteria 1</t>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Negative - Missing required fields</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Omit required health data</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Attempt to proceed without entering all required fields</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>System displays validation errors for missing fields</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- TS_020: Verify that the "You have no upcoming appointments." message is displayed when all existing appointments are past appointments or cancelled appointments whose scheduled times have already passed (Covers Acceptance Criteria 3</t>
+          <t>TC011</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>US32273</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>| User Story ID | Title | Scenario | Step # | Test Step | Expected Result | | --- | --- | --- | --- | --- | --- |</t>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Edge - Extreme cost preferences</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Premium: $0, Deductible: $0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Enter extreme values and submit</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>System processes and displays only plans meeting criteria, or a message if none available</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_001: Verify that a logged-in patient can navigate to the "My Appointments" page and view all upcoming appointments associated with their account</t>
+          <t>TC012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sorted by appointment date and time in ascending order | 1 | Log in to the patient portal with valid credentials for a patient account that has multiple upcoming appointments and at least one appointment owned by another patient in test data. | Login is successful and the patient portal home page is displayed. |</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Verify demographic and health needs input</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Age: 40, Location: OH, Doctor: Dr. Adams, Medication: Lisinopril</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Navigate to demographic input page</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>System displays fields for age, location, doctors, medications</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_001: Verify that a logged-in patient can navigate to the "My Appointments" page and view all upcoming appointments associated with their account</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sorted by appointment date and time in ascending order | 2 | Navigate to the "My Appointments" page from the patient portal. | The "My Appointments" page opens successfully. |</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Enter data and submit</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>System validates and accepts input, proceeding to recommendations</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_001: Verify that a logged-in patient can navigate to the "My Appointments" page and view all upcoming appointments associated with their account</t>
+          <t>TC013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sorted by appointment date and time in ascending order | 3 | Review the displayed appointment list. | All upcoming appointments associated with the logged-in patient account are displayed. No appointments for any other patient account are shown. |</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Negative - Invalid age</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Age: -1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Enter invalid age and submit</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>System displays error: "Invalid age"</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_001: Verify that a logged-in patient can navigate to the "My Appointments" page and view all upcoming appointments associated with their account</t>
+          <t>TC014</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sorted by appointment date and time in ascending order | 4 | Compare the displayed appointment sequence against the underlying appointment date and time values. | Appointments are sorted in ascending order by appointment date and time. |</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Edge - Maximum field length</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Doctor name: 100+ characters</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Enter maximum length for doctor name and submit</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>System accepts or displays appropriate error without crashing</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_002: Verify that each displayed upcoming appointment includes the doctor's name</t>
+          <t>TC015</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>US32306</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>appointment date</t>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verify profile view</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>User with profile data</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Navigate to profile page</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>System displays correct profile information</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_002: Verify that each displayed upcoming appointment includes the doctor's name</t>
+          <t>TC016</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>US32307</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>appointment date</t>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Verify settings update</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>New notification preference</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Go to settings, change preference, save</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>System updates and confirms setting change</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_002: Verify that each displayed upcoming appointment includes the doctor's name</t>
+          <t>TC017</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>US32308</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>appointment date</t>
+          <t>Transaction History</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verify transaction history view</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>User with transaction history</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Navigate to transaction history</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>System displays all past transactions</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_002: Verify that each displayed upcoming appointment includes the doctor's name</t>
+          <t>TC018</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>specialty</t>
+          <t>US32309</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>appointment date | 1571 | Display Upcoming Patient Appointments | TS_003: Verify that appointment date and time are displayed in the logged-in user's local time zone for all upcoming appointments | 1 | Configure or use a patient account with a known local time zone setting and upcoming appointments stored in the source system with reference times. | Test data is available with known appointment times for validation. | | 1571 | Display Upcoming Patient Appointments | TS_003: Verify that appointment date and time are displayed in the logged-in user's local time zone for all upcoming appointments | 2 | Log in to the patient portal with the selected patient account and navigate to the "My Appointments" page. | The "My Appointments" page loads successfully with upcoming appointments displayed. | | 1571 | Display Upcoming Patient Appointments | TS_003: Verify that appointment date and time are displayed in the logged-in user's local time zone for all upcoming appointments | 3 | Review the displayed date and time for each upcoming appointment. | Each appointment date and time is presented in the logged-in user's local time zone. | | 1571 | Display Upcoming Patient Appointments | TS_003: Verify that appointment date and time are displayed in the logged-in user's local time zone for all upcoming appointments | 4 | Compare the displayed local date and time values to the expected converted local values from the source appointment data. | All displayed date and time values match the expected local time zone conversion. | | 1571 | Display Upcoming Patient Appointments | TS_004: Verify that a cancelled upcoming appointment remains visible in the upcoming appointments list until its scheduled appointment time has passed and is marked with status "Cancelled" | 1 | Prepare or identify a patient account with a cancelled appointment whose scheduled appointment time is still in the future. | Valid test data exists for a cancelled future appointment. | | 1571 | Display Upcoming Patient Appointments | TS_004: Verify that a cancelled upcoming appointment remains visible in the upcoming appointments list until its scheduled appointment time has passed and is marked with status "Cancelled" | 2 | Log in to the patient portal with the patient account and navigate to the "My Appointments" page before the scheduled appointment time passes. | The "My Appointments" page opens successfully. | | 1571 | Display Upcoming Patient Appointments | TS_004: Verify that a cancelled upcoming appointment remains visible in the upcoming appointments list until its scheduled appointment time has passed and is marked with status "Cancelled" | 3 | Locate the cancelled appointment in the upcoming appointments list. | The cancelled appointment remains visible in the list. | | 1571 | Display Upcoming Patient Appointments | TS_004: Verify that a cancelled upcoming appointment remains visible in the upcoming appointments list until its scheduled appointment time has passed and is marked with status "Cancelled" | 4 | Review the status shown for the cancelled appointment. | The appointment status is displayed as "Cancelled". | | 1571 | Display Upcoming Patient Appointments | TS_005: Verify that online check-in is not available for appointments with status "Cancelled" while other valid upcoming appointments continue to display according to business rules | 1 | Prepare or identify a patient account with at least one cancelled upcoming appointment and at least one non-cancelled upcoming appointment. | Test data includes both cancelled and valid upcoming appointments. | | 1571 | Display Upcoming Patient Appointments | TS_005: Verify that online check-in is not available for appointments with status "Cancelled" while other valid upcoming appointments continue to display according to business rules | 2 | Log in to the patient portal and open the "My Appointments" page. | The appointments page loads successfully and displays upcoming appointments. | | 1571 | Display Upcoming Patient Appointments | TS_005: Verify that online check-in is not available for appointments with status "Cancelled" while other valid upcoming appointments continue to display according to business rules | 3 | Review the cancelled appointment entry for available actions. | No online check-in option is available for the cancelled appointment. | | 1571 | Display Upcoming Patient Appointments | TS_005: Verify that online check-in is not available for appointments with status "Cancelled" while other valid upcoming appointments continue to display according to business rules | 4 | Review the remaining valid upcoming appointment entries. | Other valid upcoming appointments continue to display in accordance with business rules. |</t>
+          <t>Search and Filter</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Verify data search and filter</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Search: "Diabetes", Filter: Date range</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Enter search term and filter</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>System returns correct filtered data</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_006: Verify that the appointments page displays the statuses Confirmed</t>
+          <t>TC019</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>US32310</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>and Cancelled correctly based on the latest information returned by the scheduling system | 1 | Prepare or identify a patient account with upcoming appointments having statuses Confirmed</t>
+          <t>Export Reports</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Verify report export</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Report: Claims</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Click export on claims report</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>System downloads report in selected format</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_006: Verify that the appointments page displays the statuses Confirmed</t>
+          <t>TC020</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>US32311</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>and Cancelled correctly based on the latest information returned by the scheduling system | 2 | Log in to the patient portal and navigate to the "My Appointments" page. | The appointments page opens successfully. |</t>
+          <t>User Permissions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verify permission management</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Admin user logged in</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Assign 'Editor' to user X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Navigate to permissions, assign role</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>System saves and reflects new permission</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_006: Verify that the appointments page displays the statuses Confirmed</t>
+          <t>TC021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>US32312</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>and Cancelled correctly based on the latest information returned by the scheduling system | 3 | Inspect the displayed status for each appointment. | The statuses Confirmed</t>
+          <t>System Logs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Verify system log view</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Admin user logged in</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Any log record</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Navigate to system logs</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>System displays logs with timestamp, user, action</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_006: Verify that the appointments page displays the statuses Confirmed</t>
+          <t>TC022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>US32304</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>and Cancelled correctly based on the latest information returned by the scheduling system | 4 | Compare each displayed status to the latest information returned by the scheduling system. | Every displayed status matches the latest source system status. | | 1571 | Display Upcoming Patient Appointments | TS_007: Verify that a patient with no upcoming appointments sees the message "You have no upcoming appointments." on the "My Appointments" page | 1 | Log in to the patient portal with valid credentials for a patient account that has no upcoming appointments. | Login is successful and the patient portal home page is displayed. | | 1571 | Display Upcoming Patient Appointments | TS_007: Verify that a patient with no upcoming appointments sees the message "You have no upcoming appointments." on the "My Appointments" page | 2 | Navigate to the "My Appointments" page. | The page opens successfully. | | 1571 | Display Upcoming Patient Appointments | TS_007: Verify that a patient with no upcoming appointments sees the message "You have no upcoming appointments." on the "My Appointments" page | 3 | Review the page content where upcoming appointments would normally be listed. | The message "You have no upcoming appointments." is displayed. | | 1571 | Display Upcoming Patient Appointments | TS_007: Verify that a patient with no upcoming appointments sees the message "You have no upcoming appointments." on the "My Appointments" page | 4 | Confirm that no appointment rows or cards are shown in the upcoming appointments section. | No upcoming appointment entries are displayed with the message. | | 1571 | Display Upcoming Patient Appointments | TS_008: Verify that past appointments are not displayed in the "Upcoming Appointments" list even if they exist in the patient's appointment history | 1 | Prepare or identify a patient account with both past appointments and future upcoming appointments in appointment history. | Test data includes both past and upcoming appointments. | | 1571 | Display Upcoming Patient Appointments | TS_008: Verify that past appointments are not displayed in the "Upcoming Appointments" list even if they exist in the patient's appointment history | 2 | Log in to the patient portal and navigate to the "My Appointments" page. | The "My Appointments" page loads successfully. | | 1571 | Display Upcoming Patient Appointments | TS_008: Verify that past appointments are not displayed in the "Upcoming Appointments" list even if they exist in the patient's appointment history | 3 | Review the appointments displayed in the upcoming appointments list. | Only appointments whose scheduled date and time are still upcoming are shown. | | 1571 | Display Upcoming Patient Appointments | TS_008: Verify that past appointments are not displayed in the "Upcoming Appointments" list even if they exist in the patient's appointment history | 4 | Compare the displayed list with known past appointment records for the patient. | Past appointments are not displayed in the upcoming appointments list. | | 1571 | Display Upcoming Patient Appointments | TS_009: Verify that a logged-in user cannot view appointments belonging to another patient account when accessing the appointments page | 1 | Prepare two patient accounts with distinct appointment data. | Separate appointment data exists for each patient account. | | 1571 | Display Upcoming Patient Appointments | TS_009: Verify that a logged-in user cannot view appointments belonging to another patient account when accessing the appointments page | 2 | Log in to the portal with Patient A credentials and navigate to the "My Appointments" page. | The appointments page for Patient A loads successfully. | | 1571 | Display Upcoming Patient Appointments | TS_009: Verify that a logged-in user cannot view appointments belonging to another patient account when accessing the appointments page | 3 | Review the displayed appointments and compare them with Patient B appointment records. | Only appointments associated with Patient A are visible. No Patient B appointments are shown. | | 1571 | Display Upcoming Patient Appointments | TS_009: Verify that a logged-in user cannot view appointments belonging to another patient account when accessing the appointments page | 4 | Refresh the page and verify the displayed data remains scoped to Patient A. | The page continues to show only Patient A appointments. |</t>
+          <t>Password Reset</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Verify password reset</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>User on login page</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Registered email</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Click 'Forgot Password', enter email</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>System sends reset link to email</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_010: Verify system behavior when appointment status information changes in the scheduling system before page load</t>
+          <t>TC023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ensuring the portal reflects the latest status rather than stale data | 1 | Prepare an upcoming appointment for a patient and update its status in the scheduling system immediately before loading the portal page. | The appointment has a newly updated status in the scheduling system. |</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>US32305</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Two-Factor Authentication</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Verify 2FA enablement</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Valid phone number</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Navigate to security, enable 2FA</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>System sends code and confirms setup</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_010: Verify system behavior when appointment status information changes in the scheduling system before page load</t>
+          <t>TC024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ensuring the portal reflects the latest status rather than stale data | 2 | Log in to the patient portal with the associated patient account. | Login is successful. |</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>US32303</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Verify email login</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>User is registered</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Valid email/password</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Enter credentials, click login</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>System authenticates and redirects to dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_010: Verify system behavior when appointment status information changes in the scheduling system before page load</t>
+          <t>TC025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ensuring the portal reflects the latest status rather than stale data | 3 | Navigate to the "My Appointments" page after the source status update. | The appointments page loads successfully. |</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>US32983</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NEW STORY TETS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Basic smoke test</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>System available</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Access feature</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_010: Verify system behavior when appointment status information changes in the scheduling system before page load</t>
+          <t>TC026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ensuring the portal reflects the latest status rather than stale data | 4 | Review the appointment status shown in the portal and compare it to the updated scheduling system value. | The portal displays the latest updated appointment status and does not show stale status information. |</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_011: Verify system behavior when one or more appointment detail fields are missing or incomplete from the source system</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ensuring the page handles the data gracefully without exposing incorrect appointment information | 1 | Prepare or identify an upcoming appointment record with one or more non-critical detail fields missing or incomplete in the source system. | Test data exists with incomplete appointment detail values. |</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_011: Verify system behavior when one or more appointment detail fields are missing or incomplete from the source system</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ensuring the page handles the data gracefully without exposing incorrect appointment information | 2 | Log in to the patient portal and navigate to the "My Appointments" page. | The page opens successfully without application error. |</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_011: Verify system behavior when one or more appointment detail fields are missing or incomplete from the source system</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ensuring the page handles the data gracefully without exposing incorrect appointment information | 3 | Locate the appointment with incomplete source data and review how its details are displayed. | The page handles missing or incomplete data gracefully without broken layout or misleading values. |</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_011: Verify system behavior when one or more appointment detail fields are missing or incomplete from the source system</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ensuring the page handles the data gracefully without exposing incorrect appointment information | 4 | Confirm that no incorrect appointment information is inferred or displayed for the missing fields. | Missing values are not replaced with incorrect information and the rest of the appointment remains usable and readable. |</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_012: Verify system behavior when online check-in is attempted directly for a cancelled appointment</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ensuring the action is blocked | 1 | Prepare or identify a patient account with a cancelled upcoming appointment and a known direct check-in entry point such as a deep link or action endpoint. | Test data and access path are available for the cancelled appointment. |</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_012: Verify system behavior when online check-in is attempted directly for a cancelled appointment</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ensuring the action is blocked | 2 | Log in to the patient portal with the patient account. | Login is successful. |</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_012: Verify system behavior when online check-in is attempted directly for a cancelled appointment</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ensuring the action is blocked | 3 | Attempt to access the online check-in action directly for the cancelled appointment. | The system blocks the online check-in attempt for the cancelled appointment. |</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_012: Verify system behavior when online check-in is attempted directly for a cancelled appointment</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ensuring the action is blocked | 4 | Review the response message or page state after the blocked attempt. | The user remains unable to complete online check-in and receives an appropriate blocked action outcome. |</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_013: Verify system behavior when the user is authenticated but attempts to access the appointments page for a different patient context through URL manipulation</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>session switching</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>or other unauthorized means</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_013: Verify system behavior when the user is authenticated but attempts to access the appointments page for a different patient context through URL manipulation</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>session switching</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>or other unauthorized means</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_013: Verify system behavior when the user is authenticated but attempts to access the appointments page for a different patient context through URL manipulation</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>session switching</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>or other unauthorized means</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_013: Verify system behavior when the user is authenticated but attempts to access the appointments page for a different patient context through URL manipulation</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>session switching</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>or other unauthorized means | 1571 | Display Upcoming Patient Appointments | TS_014: Verify that the appointments page loads and displays up to 100 upcoming appointments within 3 seconds under normal network conditions | 1 | Prepare or identify a patient account with up to 100 upcoming appointments under normal network conditions. | Test data and network conditions are ready for performance validation. | | 1571 | Display Upcoming Patient Appointments | TS_014: Verify that the appointments page loads and displays up to 100 upcoming appointments within 3 seconds under normal network conditions | 2 | Log in to the patient portal with the selected patient account. | Login is successful. | | 1571 | Display Upcoming Patient Appointments | TS_014: Verify that the appointments page loads and displays up to 100 upcoming appointments within 3 seconds under normal network conditions | 3 | Start timing and navigate to the "My Appointments" page. | The page begins loading appointment content. | | 1571 | Display Upcoming Patient Appointments | TS_014: Verify that the appointments page loads and displays up to 100 upcoming appointments within 3 seconds under normal network conditions | 4 | Stop timing when all upcoming appointments are fully rendered and visible. | The page displays all appointment records within 3 seconds under normal network conditions. | | 1571 | Display Upcoming Patient Appointments | TS_015: Verify that exactly 100 upcoming appointments are displayed completely and remain sorted in ascending date/time order without truncation or duplication | 1 | Prepare or identify a patient account with exactly 100 upcoming appointments. | Test data exists with exactly 100 upcoming appointments. | | 1571 | Display Upcoming Patient Appointments | TS_015: Verify that exactly 100 upcoming appointments are displayed completely and remain sorted in ascending date/time order without truncation or duplication | 2 | Log in to the portal and open the "My Appointments" page. | The appointments page loads successfully. | | 1571 | Display Upcoming Patient Appointments | TS_015: Verify that exactly 100 upcoming appointments are displayed completely and remain sorted in ascending date/time order without truncation or duplication | 3 | Count the displayed appointment entries. | Exactly 100 upcoming appointments are displayed. |</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_015: Verify that exactly 100 upcoming appointments are displayed completely and remain sorted in ascending date/time order without truncation or duplication | 4 | Review the list for ordering</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>missing entries</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>and duplicate entries. | All 100 appointments are displayed completely in ascending date and time order without truncation or duplication. |</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_016: Verify system behavior when a patient has a single upcoming appointment</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ensuring it displays correctly with all required appointment details | 1 | Log in to the patient portal with a patient account that has exactly one upcoming appointment. | Login is successful and the patient portal home page is displayed. |</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_016: Verify system behavior when a patient has a single upcoming appointment</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>ensuring it displays correctly with all required appointment details | 2 | Navigate to the "My Appointments" page. | The page opens successfully and displays one upcoming appointment. |</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_016: Verify system behavior when a patient has a single upcoming appointment</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ensuring it displays correctly with all required appointment details | 3 | Inspect the displayed appointment details. | The appointment shows the doctor's name</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>specialty</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_016: Verify system behavior when a patient has a single upcoming appointment</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ensuring it displays correctly with all required appointment details | 4 | Confirm that no additional unexpected appointment entries are present. | Only the single valid upcoming appointment is displayed correctly. |</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_017: Verify system behavior when multiple upcoming appointments have closely spaced or identical times</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ensuring they are still displayed in ascending order consistently | 1 | Prepare or identify a patient account with multiple upcoming appointments that have closely spaced times or identical times. | Test data exists with closely spaced or identical appointment times. |</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_017: Verify system behavior when multiple upcoming appointments have closely spaced or identical times</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ensuring they are still displayed in ascending order consistently | 2 | Log in to the patient portal and navigate to the "My Appointments" page. | The appointments page loads successfully. |</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_017: Verify system behavior when multiple upcoming appointments have closely spaced or identical times</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ensuring they are still displayed in ascending order consistently | 3 | Review the order of the displayed appointments. | Appointments are displayed in consistent ascending order based on date and time. |</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_017: Verify system behavior when multiple upcoming appointments have closely spaced or identical times</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>ensuring they are still displayed in ascending order consistently | 4 | Refresh the page and verify the ordering again. | The ordering remains stable and consistent after refresh. |</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_018: Verify that a cancelled appointment is visible immediately before its scheduled appointment time and no longer appears once that scheduled time has passed</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>in accordance with upcoming appointment rules | 1 | Prepare or identify a cancelled appointment whose scheduled time is approaching but has not yet passed. | A cancelled appointment exists for time-based validation. |</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_018: Verify that a cancelled appointment is visible immediately before its scheduled appointment time and no longer appears once that scheduled time has passed</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>in accordance with upcoming appointment rules | 2 | Log in before the scheduled appointment time and navigate to the "My Appointments" page. | The appointments page loads successfully. |</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_018: Verify that a cancelled appointment is visible immediately before its scheduled appointment time and no longer appears once that scheduled time has passed</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>in accordance with upcoming appointment rules | 3 | Locate the cancelled appointment in the upcoming appointments list. | The cancelled appointment is visible immediately before its scheduled time and shows status "Cancelled". |</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_018: Verify that a cancelled appointment is visible immediately before its scheduled appointment time and no longer appears once that scheduled time has passed</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>in accordance with upcoming appointment rules | 4 | After the scheduled appointment time passes</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>refresh the "My Appointments" page and review the list again. | The cancelled appointment no longer appears in the upcoming appointments list after its scheduled time has passed. |</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_019: Verify that appointments occurring near local time zone boundaries</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>such as midnight or daylight saving time changes</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>are displayed with the correct local date/time and are classified correctly as upcoming or past | 1 | Prepare or identify appointment data occurring near midnight or daylight saving time transitions for a patient with a known local time zone. | Boundary time zone test data is available. |</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_019: Verify that appointments occurring near local time zone boundaries</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>such as midnight or daylight saving time changes</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>are displayed with the correct local date/time and are classified correctly as upcoming or past | 2 | Log in to the patient portal with the selected account and navigate to the "My Appointments" page. | The appointments page opens successfully. |</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_019: Verify that appointments occurring near local time zone boundaries</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>such as midnight or daylight saving time changes</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>are displayed with the correct local date/time and are classified correctly as upcoming or past | 3 | Review the displayed local date and time for the boundary appointments. | The displayed values reflect the correct local date and time conversion for boundary conditions. |</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>| 1571 | Display Upcoming Patient Appointments | TS_019: Verify that appointments occurring near local time zone boundaries</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>such as midnight or daylight saving time changes</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>are displayed with the correct local date/time and are classified correctly as upcoming or past | 4 | Validate whether each boundary appointment appears or is excluded based on whether it is locally upcoming or past. | Each appointment is classified correctly as upcoming or past according to the user's local time zone. | | 1571 | Display Upcoming Patient Appointments | TS_020: Verify that the "You have no upcoming appointments." message is displayed when all existing appointments are past appointments or cancelled appointments whose scheduled times have already passed | 1 | Prepare or identify a patient account where all appointments are either past appointments or cancelled appointments whose scheduled times have already passed. | Test data exists with no qualifying upcoming appointments. | | 1571 | Display Upcoming Patient Appointments | TS_020: Verify that the "You have no upcoming appointments." message is displayed when all existing appointments are past appointments or cancelled appointments whose scheduled times have already passed | 2 | Log in to the patient portal with the patient account and navigate to the "My Appointments" page. | The "My Appointments" page loads successfully. | | 1571 | Display Upcoming Patient Appointments | TS_020: Verify that the "You have no upcoming appointments." message is displayed when all existing appointments are past appointments or cancelled appointments whose scheduled times have already passed | 3 | Review the content of the upcoming appointments section. | No appointment entries are displayed in the upcoming appointments section. | | 1571 | Display Upcoming Patient Appointments | TS_020: Verify that the "You have no upcoming appointments." message is displayed when all existing appointments are past appointments or cancelled appointments whose scheduled times have already passed | 4 | Verify the informational message shown to the user. | The message "You have no upcoming appointments." is displayed. |</t>
+          <t>US32744</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>member 1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Basic smoke test</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>System available</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Access feature</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
         </is>
       </c>
     </row>
